--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R5910a94adbd84fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Rb674117e06e248d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R35d1ef8741d04e5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R15515415f59e4bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Re7ff9a2a3877411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R3f3dbb97b50f4c3d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,27 +15,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="18"/>
+      <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:i/>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="FF17365D"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -118,15 +112,15 @@
       <x:alignment horizontal="left"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -136,7 +130,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -389,7 +383,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Modbus485Emulator External Test Results</x:v>
+        <x:v>Modbus485Emulator v0.1.0 External Test Results</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -487,7 +481,7 @@
         <x:v>CANalyzer 9.x SP8 x86</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
-        <x:v>상대경로 3개 설정 후 비동기 Refresh Polling</x:v>
+        <x:v>DeviceMap/FrameRule 두 상대경로와 참조 Register Map 준비 후 비동기 Refresh Polling</x:v>
       </x:c>
       <x:c r="F6" s="16" t="str">
         <x:v>Disconnected, ConfigurationValid=1, LastResult=0</x:v>
@@ -504,19 +498,19 @@
         <x:v>EV-003</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>7/8</x:v>
+        <x:v>7/8/9</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
-        <x:v>FR-PORT-007~017, TBD-038</x:v>
+        <x:v>FR-PORT-007~020, TBD-038</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>CANalyzer + Multi USB 485</x:v>
       </x:c>
       <x:c r="E7" s="16" t="str">
-        <x:v>두 COM Port 전체 Connect</x:v>
+        <x:v>1~4개 활성 COM Port 전체 Connect와 CAPL/CSV 활성 Port 수 확인</x:v>
       </x:c>
       <x:c r="F7" s="16" t="str">
-        <x:v>두 Port가 모두 열릴 때만 Connected; 일부 실패 시 전체 Rollback</x:v>
+        <x:v>모든 활성 Port가 열릴 때만 Connected; 일부 실패 시 전체 Rollback; ActivePortCount와 Device CSV 고유 Port 수 일치</x:v>
       </x:c>
       <x:c r="G7" s="16" t="str"/>
       <x:c r="H7" s="16" t="str">
@@ -692,13 +686,13 @@
         <x:v>FR-CAN-034~041</x:v>
       </x:c>
       <x:c r="D14" s="16" t="str">
-        <x:v>Two virtual CAN channels</x:v>
+        <x:v>1~4 virtual CAN channels</x:v>
       </x:c>
       <x:c r="E14" s="16" t="str">
-        <x:v>두 Port 동시 Change Burst</x:v>
+        <x:v>여러 활성 Port 동시 Change Burst</x:v>
       </x:c>
       <x:c r="F14" s="16" t="str">
-        <x:v>Port Round-robin, Port 내부 FIFO, Snapshot 묶음 비분할</x:v>
+        <x:v>활성 Port Round-robin, Port 내부 FIFO, Snapshot 묶음 비분할</x:v>
       </x:c>
       <x:c r="G14" s="16" t="str"/>
       <x:c r="H14" s="16" t="str">
@@ -733,7 +727,7 @@
       <x:c r="I15" s="16" t="str"/>
       <x:c r="J15" s="16" t="str"/>
     </x:row>
-    <x:row r="16" ht="15" hidden="0" customHeight="1">
+    <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="17" t="str">
         <x:v>EV-012</x:v>
       </x:c>
@@ -747,10 +741,10 @@
         <x:v>CANalyzer Panel</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
-        <x:v>Manual Read/Write 및 1초 AutoRead</x:v>
+        <x:v>Manual Write Data[122] 및 Signal Control</x:v>
       </x:c>
       <x:c r="F16" s="16" t="str">
-        <x:v>확정 요청 Snapshot 사용, word 범위 검증, ResultCode 표시</x:v>
+        <x:v>Send 시 요청 Snapshot 사용, Quantity 1~122와 word 범위 검증, ResultCode 표시</x:v>
       </x:c>
       <x:c r="G16" s="16" t="str"/>
       <x:c r="H16" s="16" t="str">
@@ -776,7 +770,7 @@
         <x:v>Signal Float/Signed Read/Write</x:v>
       </x:c>
       <x:c r="F17" s="16" t="str">
-        <x:v>12.5 등 물리값 왕복, 실패 시 기존 출력 유지</x:v>
+        <x:v>12.5 등 물리값 왕복, 실패 시 현재 출력 유지</x:v>
       </x:c>
       <x:c r="G17" s="16" t="str"/>
       <x:c r="H17" s="16" t="str">
@@ -785,7 +779,7 @@
       <x:c r="I17" s="16" t="str"/>
       <x:c r="J17" s="16" t="str"/>
     </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
+    <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="17" t="str">
         <x:v>EV-014</x:v>
       </x:c>
@@ -802,7 +796,7 @@
         <x:v>한 USB-RS485 Port 제거 후 복구</x:v>
       </x:c>
       <x:c r="F18" s="16" t="str">
-        <x:v>전체 정리 후 3초 간격 최대 10회; 복구 시 두 Port Connected</x:v>
+        <x:v>전체 정리 후 3초 간격 최대 10회; 복구 시 모든 활성 Port Connected</x:v>
       </x:c>
       <x:c r="G18" s="16" t="str"/>
       <x:c r="H18" s="16" t="str">
@@ -837,24 +831,24 @@
       <x:c r="I19" s="16" t="str"/>
       <x:c r="J19" s="16" t="str"/>
     </x:row>
-    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" s="17" t="str">
         <x:v>EV-016</x:v>
       </x:c>
       <x:c r="B20" s="16" t="str">
-        <x:v>9/10</x:v>
+        <x:v>6/9/10</x:v>
       </x:c>
       <x:c r="C20" s="16" t="str">
-        <x:v>PERF-004~021, TBD-027, TBD-030, TBD-039</x:v>
+        <x:v>PERF-004~021, LOG-011~017, REQ-DIAG-002, TBD-027, TBD-030, TBD-039</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
         <x:v>200 Rule stress profile</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
-        <x:v>200 Rule, Quantity 125, 0x81 Burst</x:v>
+        <x:v>200 Rule, Quantity 125, 0x81 Burst 및 Error Queue overflow</x:v>
       </x:c>
       <x:c r="F20" s="16" t="str">
-        <x:v>RTU 영향 없이 0x81 100ms/0x80 1000ms 목표와 bounded Queue 진단</x:v>
+        <x:v>RTU 영향 없이 0x81 100ms/0x80 1000ms 목표를 유지하고 DropCount 또는 OverflowLatch 변화 시 CAPL이 Pending/Capacity/High-water를 한 번 진단</x:v>
       </x:c>
       <x:c r="G20" s="16" t="str"/>
       <x:c r="H20" s="16" t="str">
@@ -925,120 +919,182 @@
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Git Commit</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="str"/>
-      <x:c r="D4" s="16" t="str"/>
+        <x:v>Release Version</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>0.1.0</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Release Baseline</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B5" s="16" t="str">
-        <x:v>M485E.dll SHA-256</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str"/>
-      <x:c r="D5" s="16" t="str"/>
+        <x:v>Baseline Date</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>docs/REQUIREMENTS_SPEC.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="16" t="str">
-        <x:v>CANalyzer</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>Version / Service Pack</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="str">
-        <x:v>CANalyzer 9.x SP8 x86</x:v>
-      </x:c>
+        <x:v>Git Commit</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str"/>
       <x:c r="D6" s="16" t="str"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="16" t="str">
-        <x:v>Vector</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>Driver / License</x:v>
+        <x:v>M485E.dll SHA-256</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str"/>
       <x:c r="D7" s="16" t="str"/>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A8" s="16" t="str">
-        <x:v>Adapter</x:v>
+        <x:v>Baseline</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>Model</x:v>
+        <x:v>Generated Contracts</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>SystemBase Multi USB 485</x:v>
+        <x:v>ErrorCodes=90; PublicConstants=185</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
-        <x:v>Automatic direction control</x:v>
+        <x:v>tests/contracts/Test-M485EContractGeneration.ps1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
-        <x:v>Serial Port 0</x:v>
+        <x:v>CANalyzer</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
-        <x:v>COM / Baud / Data / Parity / Stop</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="str"/>
+        <x:v>Version / Service Pack</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>CANalyzer 9.x SP8 x86</x:v>
+      </x:c>
       <x:c r="D9" s="16" t="str"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="16" t="str">
-        <x:v>Serial Port 1</x:v>
+        <x:v>Vector</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
-        <x:v>COM / Baud / Data / Parity / Stop</x:v>
+        <x:v>Driver / License</x:v>
       </x:c>
       <x:c r="C10" s="16" t="str"/>
       <x:c r="D10" s="16" t="str"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
-        <x:v>Board</x:v>
+        <x:v>Adapter</x:v>
       </x:c>
       <x:c r="B11" s="16" t="str">
-        <x:v>Model / Firmware</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="str"/>
-      <x:c r="D11" s="16" t="str"/>
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>SystemBase Multi USB 485</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>Automatic direction control</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="16" t="str">
-        <x:v>Board</x:v>
+        <x:v>Serial Port 0</x:v>
       </x:c>
       <x:c r="B12" s="16" t="str">
-        <x:v>Modbus Master Response Timeout</x:v>
+        <x:v>COM / Baud / Data / Parity / Stop</x:v>
       </x:c>
       <x:c r="C12" s="16" t="str"/>
-      <x:c r="D12" s="16" t="str">
-        <x:v>ms</x:v>
-      </x:c>
+      <x:c r="D12" s="16" t="str"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>CAN</x:v>
+        <x:v>Serial Port 1</x:v>
       </x:c>
       <x:c r="B13" s="16" t="str">
-        <x:v>Channel mapping</x:v>
-      </x:c>
-      <x:c r="C13" s="16" t="str">
-        <x:v>PortSlot 0→Virtual CAN 1; PortSlot 1→Virtual CAN 2</x:v>
-      </x:c>
+        <x:v>COM / Baud / Data / Parity / Stop</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="str"/>
       <x:c r="D13" s="16" t="str"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="16" t="str">
-        <x:v>Test</x:v>
+        <x:v>Serial Port 2</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
-        <x:v>Operator / Date</x:v>
+        <x:v>COM / Baud / Data / Parity / Stop</x:v>
       </x:c>
       <x:c r="C14" s="16" t="str"/>
       <x:c r="D14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="16" t="str">
+        <x:v>Serial Port 3</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>COM / Baud / Data / Parity / Stop</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str"/>
+      <x:c r="D15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="16" t="str">
+        <x:v>Board</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Model / Firmware</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str"/>
+      <x:c r="D16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="16" t="str">
+        <x:v>Board</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="str">
+        <x:v>Modbus Master Response Timeout</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="str"/>
+      <x:c r="D17" s="16" t="str">
+        <x:v>ms</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="16" t="str">
+        <x:v>CAN</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="str">
+        <x:v>Channel mapping</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="str">
+        <x:v>PortSlot 0~3→Virtual CAN 1~4 (활성 Port만)</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="16" t="str">
+        <x:v>Test</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="str">
+        <x:v>Operator / Date</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="str"/>
+      <x:c r="D19" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R15515415f59e4bcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Re7ff9a2a3877411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R3f3dbb97b50f4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R6d82b3a9a5984069"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R738cad2d2e3749df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Rea7eb35be2f34b32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,7 +383,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Modbus485Emulator v0.1.0 External Test Results</x:v>
+        <x:v>Modbus485Emulator v0.2.0 External Test Results</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -449,16 +449,16 @@
         <x:v>1/2</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>IF-API-001~021, COMP-001, COMP-015</x:v>
+        <x:v>IF-API-001~021, COMP-001, COMP-002, COMP-015</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>CANalyzer 9.x SP8 x86</x:v>
+        <x:v>CANalyzer 9.x SP8 x86 / CANalyzer 18 x64</x:v>
       </x:c>
       <x:c r="E5" s="16" t="str">
-        <x:v>CAPL Compile 및 #pragma library 로드</x:v>
+        <x:v>CAPL Compile 및 직접 DLL/.vmodule 로드</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>21개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
+        <x:v>두 환경에서 21개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str"/>
       <x:c r="H5" s="16" t="str">
@@ -922,7 +922,7 @@
         <x:v>Release Version</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>0.1.0</x:v>
+        <x:v>0.2.0</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
         <x:v>Release Baseline</x:v>
@@ -984,7 +984,7 @@
         <x:v>Version / Service Pack</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str">
-        <x:v>CANalyzer 9.x SP8 x86</x:v>
+        <x:v>CANalyzer 9.x SP8 x86 / CANalyzer 18 x64</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str"/>
     </x:row>

--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R6d82b3a9a5984069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R738cad2d2e3749df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Rea7eb35be2f34b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="Rc1a011c3c8e74484"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Rdf2713a89a96435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Rf128fa516d3e42e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,7 +383,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Modbus485Emulator v0.2.0 External Test Results</x:v>
+        <x:v>Modbus485Emulator v0.3.0 External Test Results</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -449,7 +449,7 @@
         <x:v>1/2</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>IF-API-001~021, COMP-001, COMP-002, COMP-015</x:v>
+        <x:v>IF-API-001~026, COMP-001, COMP-002, COMP-015</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
         <x:v>CANalyzer 9.x SP8 x86 / CANalyzer 18 x64</x:v>
@@ -458,7 +458,7 @@
         <x:v>CAPL Compile 및 직접 DLL/.vmodule 로드</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>두 환경에서 21개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
+        <x:v>두 환경에서 26개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str"/>
       <x:c r="H5" s="16" t="str">
@@ -856,13 +856,65 @@
       </x:c>
       <x:c r="I20" s="16" t="str"/>
       <x:c r="J20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A21" s="17" t="str">
+        <x:v>EV-017</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>5/7/10</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="str">
+        <x:v>FR-RTU-036~039, FR-UI-019~020</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="str">
+        <x:v>CANalyzer Panel + Board + Serial trace</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="str">
+        <x:v>Index별 RTU 통신 OFF/ON</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="str">
+        <x:v>비활성 Index는 FC03/04/10 무응답·무변경; 동일 Port의 다른 Slave와 Direct/CAN은 유지; Refresh 성공 후 활성화</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="str"/>
+      <x:c r="H21" s="16" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="I21" s="16" t="str"/>
+      <x:c r="J21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A22" s="17" t="str">
+        <x:v>EV-018</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="str">
+        <x:v>7/10</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="str">
+        <x:v>FR-UI-021, LOG-018~024, IF-API-024~026</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="str">
+        <x:v>CANalyzer Panel + CSV</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="str">
+        <x:v>RTU Log OFF→ON, 정상·무응답·용량 경계</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="str">
+        <x:v>새 파일 생성; REQ/RES 또는 REQ/NO_RES 동일 Sequence; 12 Column·전체 ADU·DroppedCount·ActiveLed 확인</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="str"/>
+      <x:c r="H22" s="16" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="I22" s="16" t="str"/>
+      <x:c r="J22" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H20">
+  <x:conditionalFormatting sqref="H5:H22">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <x:formula>"PASS"</x:formula>
     </x:cfRule>
@@ -874,7 +926,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H5:H20">
+    <x:dataValidation type="list" sqref="H5:H22">
       <x:formula1>"Not Tested,PASS,FAIL,Blocked,N/A"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -922,7 +974,7 @@
         <x:v>Release Version</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>0.2.0</x:v>
+        <x:v>0.3.0</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
         <x:v>Release Baseline</x:v>
@@ -970,7 +1022,7 @@
         <x:v>Generated Contracts</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>ErrorCodes=90; PublicConstants=185</x:v>
+        <x:v>ErrorCodes=92; PublicConstants=207</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
         <x:v>tests/contracts/Test-M485EContractGeneration.ps1</x:v>
@@ -1135,8 +1187,8 @@
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$20,A4)</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A4)</x:f>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1144,7 +1196,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$20,A5)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A5)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1153,7 +1205,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$20,A6)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1162,7 +1214,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$20,A7)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1171,7 +1223,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$20,A8)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A8)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="Rc1a011c3c8e74484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Rdf2713a89a96435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Rf128fa516d3e42e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="Rfe2a95d5168544a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Rb366d6a005ad4182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R0578d06e22fe49ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -449,7 +449,7 @@
         <x:v>1/2</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>IF-API-001~026, COMP-001, COMP-002, COMP-015</x:v>
+        <x:v>IF-API-001~027, COMP-001, COMP-002, COMP-015</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
         <x:v>CANalyzer 9.x SP8 x86 / CANalyzer 18 x64</x:v>
@@ -458,7 +458,7 @@
         <x:v>CAPL Compile 및 직접 DLL/.vmodule 로드</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>두 환경에서 26개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
+        <x:v>두 환경에서 27개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str"/>
       <x:c r="H5" s="16" t="str">
@@ -883,7 +883,7 @@
       <x:c r="I21" s="16" t="str"/>
       <x:c r="J21" s="16" t="str"/>
     </x:row>
-    <x:row r="22" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="22" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A22" s="17" t="str">
         <x:v>EV-018</x:v>
       </x:c>
@@ -891,16 +891,16 @@
         <x:v>7/10</x:v>
       </x:c>
       <x:c r="C22" s="16" t="str">
-        <x:v>FR-UI-021, LOG-018~024, IF-API-024~026</x:v>
+        <x:v>FR-UI-021, LOG-018~024, IF-API-024~027</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
         <x:v>CANalyzer Panel + CSV</x:v>
       </x:c>
       <x:c r="E22" s="16" t="str">
-        <x:v>RTU Log OFF→ON, 정상·무응답·용량 경계</x:v>
+        <x:v>RTU Log OFF→ON, 정상·무응답·용량·종료 경계</x:v>
       </x:c>
       <x:c r="F22" s="16" t="str">
-        <x:v>새 파일 생성; REQ/RES 또는 REQ/NO_RES 동일 Sequence; 12 Column·전체 ADU·DroppedCount·ActiveLed 확인</x:v>
+        <x:v>파일 Open 후 Capture; REQ/RES 또는 REQ/NO_RES 동일 Sequence; 12 Column·전체 ADU·DroppedCount·2초 idle wait·ActiveLed 확인</x:v>
       </x:c>
       <x:c r="G22" s="16" t="str"/>
       <x:c r="H22" s="16" t="str">
@@ -988,7 +988,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-08-13</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
         <x:v>docs/REQUIREMENTS_SPEC.md</x:v>
@@ -1022,7 +1022,7 @@
         <x:v>Generated Contracts</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>ErrorCodes=92; PublicConstants=207</x:v>
+        <x:v>ErrorCodes=93; PublicConstants=210</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
         <x:v>tests/contracts/Test-M485EContractGeneration.ps1</x:v>

--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="Rfe2a95d5168544a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="Rb366d6a005ad4182"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R0578d06e22fe49ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R51e2cfbce993420e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R2983e747c12e4a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R5c249986bb3645f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,7 +383,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Modbus485Emulator v0.3.0 External Test Results</x:v>
+        <x:v>Modbus485Emulator v0.4.0 External Test Results</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -449,7 +449,7 @@
         <x:v>1/2</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>IF-API-001~027, COMP-001, COMP-002, COMP-015</x:v>
+        <x:v>IF-API-001~008, IF-API-011, IF-API-014~027, COMP-001, COMP-002, COMP-015</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
         <x:v>CANalyzer 9.x SP8 x86 / CANalyzer 18 x64</x:v>
@@ -458,7 +458,7 @@
         <x:v>CAPL Compile 및 직접 DLL/.vmodule 로드</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>두 환경에서 27개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
+        <x:v>두 환경에서 23개 API가 중복·누락 없이 Compile되고 Measurement가 시작됨</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str"/>
       <x:c r="H5" s="16" t="str">
@@ -588,7 +588,7 @@
         <x:v>FC10 정상·동일값·권한 공백 Write</x:v>
       </x:c>
       <x:c r="F10" s="16" t="str">
-        <x:v>원자 적용; 동일값 Snapshot 없음; 공백은 0x02 및 무변경</x:v>
+        <x:v>원자 적용; 다음 선택된 0x80에 최종값 반영; 공백은 0x02 및 무변경</x:v>
       </x:c>
       <x:c r="G10" s="16" t="str"/>
       <x:c r="H10" s="16" t="str">
@@ -637,10 +637,10 @@
         <x:v>CANalyzer virtual CAN</x:v>
       </x:c>
       <x:c r="E12" s="16" t="str">
-        <x:v>Periodic Snapshot Quantity 6</x:v>
+        <x:v>Periodic Rule Data Quantity 6</x:v>
       </x:c>
       <x:c r="F12" s="16" t="str">
-        <x:v>0x80 Header 1 + Data 2, 마지막 DLC 4</x:v>
+        <x:v>0x80 Header 1 + Data 2, Header Byte 3=0, 마지막 DLC 4</x:v>
       </x:c>
       <x:c r="G12" s="16" t="str"/>
       <x:c r="H12" s="16" t="str">
@@ -649,7 +649,7 @@
       <x:c r="I12" s="16" t="str"/>
       <x:c r="J12" s="16" t="str"/>
     </x:row>
-    <x:row r="13" ht="15" hidden="0" customHeight="1">
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A13" s="17" t="str">
         <x:v>EV-009</x:v>
       </x:c>
@@ -663,10 +663,10 @@
         <x:v>Board + Panel + CAN Trace</x:v>
       </x:c>
       <x:c r="E13" s="16" t="str">
-        <x:v>RTU/Direct/Reset 변경 Snapshot</x:v>
+        <x:v>RTU/Direct/Reset 뒤 최종값 확인</x:v>
       </x:c>
       <x:c r="F13" s="16" t="str">
-        <x:v>0x81 SourceType 01/02/03 및 변경 당시 값 보존</x:v>
+        <x:v>0x81 미출력, 다음 선택된 0x80에 최종값 반영, 중간 상태 재생 없음</x:v>
       </x:c>
       <x:c r="G13" s="16" t="str"/>
       <x:c r="H13" s="16" t="str">
@@ -689,10 +689,10 @@
         <x:v>1~4 virtual CAN channels</x:v>
       </x:c>
       <x:c r="E14" s="16" t="str">
-        <x:v>여러 활성 Port 동시 Change Burst</x:v>
+        <x:v>여러 활성 Port Periodic 출력</x:v>
       </x:c>
       <x:c r="F14" s="16" t="str">
-        <x:v>활성 Port Round-robin, Port 내부 FIFO, Snapshot 묶음 비분할</x:v>
+        <x:v>활성 Port Round-robin, Rule Data 묶음 비분할, 0x80만 출력</x:v>
       </x:c>
       <x:c r="G14" s="16" t="str"/>
       <x:c r="H14" s="16" t="str">
@@ -845,10 +845,10 @@
         <x:v>200 Rule stress profile</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
-        <x:v>200 Rule, Quantity 125, 0x81 Burst 및 Error Queue overflow</x:v>
+        <x:v>200 Rule, Quantity 125, 66 Frame/Tick 및 Error Queue overflow</x:v>
       </x:c>
       <x:c r="F20" s="16" t="str">
-        <x:v>RTU 영향 없이 0x81 100ms/0x80 1000ms 목표를 유지하고 DropCount 또는 OverflowLatch 변화 시 CAPL이 Pending/Capacity/High-water를 한 번 진단</x:v>
+        <x:v>RTU 영향 없이 선택 Rule의 0x80을 1000ms Cycle로 처리하고 DropCount 또는 OverflowLatch 변화 시 CAPL이 Pending/Capacity/High-water를 한 번 진단</x:v>
       </x:c>
       <x:c r="G20" s="16" t="str"/>
       <x:c r="H20" s="16" t="str">
@@ -974,7 +974,7 @@
         <x:v>Release Version</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>0.3.0</x:v>
+        <x:v>0.4.0</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
         <x:v>Release Baseline</x:v>
@@ -1022,7 +1022,7 @@
         <x:v>Generated Contracts</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>ErrorCodes=93; PublicConstants=210</x:v>
+        <x:v>ErrorCodes=91; PublicConstants=189</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
         <x:v>tests/contracts/Test-M485EContractGeneration.ps1</x:v>

--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R51e2cfbce993420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R2983e747c12e4a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R5c249986bb3645f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R6809862edde54388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R2c2de52f5f714c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R02b912d8540d455b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,7 +383,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Modbus485Emulator v0.4.0 External Test Results</x:v>
+        <x:v>Modbus485Emulator v0.5.0 External Test Results</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -909,12 +909,38 @@
       <x:c r="I22" s="16" t="str"/>
       <x:c r="J22" s="16" t="str"/>
     </x:row>
+    <x:row r="23" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A23" s="17" t="str">
+        <x:v>EV-019</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="str">
+        <x:v>FR-UI-022~023, LOG-025~028, AC-255~257</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="str">
+        <x:v>CANalyzer Panel + CSV</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="str">
+        <x:v>Btn_ReadOption Scalar 계약과 RTU Log CAPL Output View 최근 표시</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="str">
+        <x:v>Btn_ReadOption int32 Scalar/no-handler 및 Check_ReadOption[200] 정책 유지; 전체 CSV 보존; 동일 Drain 문자열 최근 10줄을 200ms 이상 간격 Overwrite; Panel/Control 불일치에도 CSV 정상; OFF 후 마지막 표시 유지</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="str"/>
+      <x:c r="H23" s="16" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="I23" s="16" t="str"/>
+      <x:c r="J23" s="16" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H22">
+  <x:conditionalFormatting sqref="H5:H23">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <x:formula>"PASS"</x:formula>
     </x:cfRule>
@@ -926,7 +952,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H5:H22">
+    <x:dataValidation type="list" sqref="H5:H23">
       <x:formula1>"Not Tested,PASS,FAIL,Blocked,N/A"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -974,7 +1000,7 @@
         <x:v>Release Version</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>0.4.0</x:v>
+        <x:v>0.5.0</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
         <x:v>Release Baseline</x:v>
@@ -988,7 +1014,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>2026-08-13</x:v>
+        <x:v>2026-08-17</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
         <x:v>docs/REQUIREMENTS_SPEC.md</x:v>
@@ -1187,8 +1213,8 @@
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A4)</x:f>
-        <x:v>18</x:v>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A4)</x:f>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1196,7 +1222,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A5)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A5)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1205,7 +1231,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A6)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1214,7 +1240,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A7)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1223,7 +1249,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$22,A8)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A8)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
+++ b/docs/05_Test/Modbus485Emulator_External_Test_Result.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="R6809862edde54388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R2c2de52f5f714c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="R02b912d8540d455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="1" r:id="Re6fb4995f911405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Environment" sheetId="2" r:id="R3c116f8a947c49e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" r:id="Rb41c1f7ecfdd4bef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -383,7 +383,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="4" t="str">
-        <x:v>Modbus485Emulator v0.5.0 External Test Results</x:v>
+        <x:v>Modbus485Emulator v0.6.0 External Test Results</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -935,12 +935,38 @@
       <x:c r="I23" s="16" t="str"/>
       <x:c r="J23" s="16" t="str"/>
     </x:row>
+    <x:row r="24" ht="66" hidden="0" customHeight="1">
+      <x:c r="A24" s="17" t="str">
+        <x:v>EV-020</x:v>
+      </x:c>
+      <x:c r="B24" s="16" t="str">
+        <x:v>10/11</x:v>
+      </x:c>
+      <x:c r="C24" s="16" t="str">
+        <x:v>FR-DPG-001~020, AC-258~264</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="str">
+        <x:v>CANalyzer 9.x/18 Panel Designer + Sample CSV</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="str">
+        <x:v>Device Signal Panel Generator 산출물 적용 및 Device Panel 동작</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="str">
+        <x:v>Sample·회사 CSV Analyze/Generate 후 XVP GroupBox 복사, generated System Variable DB와 DevicePanel CAPL 적용·Compile; Display Update/Send Changed/Device Reset/Reset All, Raw Hex, SnapshotValid·Busy·실패 결과·비원자 경계를 확인</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="str"/>
+      <x:c r="H24" s="16" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="I24" s="16" t="str"/>
+      <x:c r="J24" s="16" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H23">
+  <x:conditionalFormatting sqref="H5:H24">
     <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <x:formula>"PASS"</x:formula>
     </x:cfRule>
@@ -952,7 +978,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H5:H23">
+    <x:dataValidation type="list" sqref="H5:H24">
       <x:formula1>"Not Tested,PASS,FAIL,Blocked,N/A"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1000,7 +1026,7 @@
         <x:v>Release Version</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
-        <x:v>0.5.0</x:v>
+        <x:v>0.6.0</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
         <x:v>Release Baseline</x:v>
@@ -1014,7 +1040,7 @@
         <x:v>Baseline Date</x:v>
       </x:c>
       <x:c r="C5" s="16" t="str">
-        <x:v>2026-08-17</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
         <x:v>docs/REQUIREMENTS_SPEC.md</x:v>
@@ -1213,8 +1239,8 @@
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A4)</x:f>
-        <x:v>19</x:v>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$24,A4)</x:f>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1222,7 +1248,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A5)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$24,A5)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1231,7 +1257,7 @@
         <x:v>FAIL</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A6)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$24,A6)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1240,7 +1266,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A7)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$24,A7)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1249,7 +1275,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:f>COUNTIF('Test Results'!$H$5:$H$23,A8)</x:f>
+        <x:f>COUNTIF('Test Results'!$H$5:$H$24,A8)</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
